--- a/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle est au jardin avec maman. Hervé est près du bac. Il parle peu. Gwenaëlle veut jouer. Maman dit : on peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Gwenaëlle tend le seau. Elle sait attendre. Hervé touche le seau. Il ne dit rien. Gwenaëlle sourit. Elle ne force pas la parole. Plus tard, Hervé dit : sable.</t>
+          <t>Gwenaëlle est au jardin avec maman. Hervé est près du bac. Il parle peu. Gwenaëlle veut jouer. On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Gwenaëlle tend le seau. Elle sait attendre. Hervé touche le seau. Il ne dit rien. Gwenaëlle sourit. Elle ne force pas la parole. Plus tard, Sable.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gwenaëlle est au jardin avec maman. Hervé est près du bac. Il parle peu. Gwenaëlle veut jouer.
+maman|On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole.
+narrateur|Gwenaëlle tend le seau. Elle sait attendre. Hervé touche le seau. Il ne dit rien. Gwenaëlle sourit. Elle ne force pas la parole. Plus tard,
+copain|Sable.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hervé parle peu. Que fait Gwenaëlle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gwenaëlle a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le seau. Gwenaëlle donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 copain|Sable.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Hervé parle peu. Que fait Gwenaëlle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Gwenaëlle a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Maman range le seau. Gwenaëlle donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gwenaëlle tend un jouet et attend</t>
+          <t>La pelle jaune près des pots</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DIF.BES.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une pelle jaune attend près des pots. Chouchou la tend à Mila, qui parle peu. Ils font un petit tas de terre. Mila dit : terre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle est au jardin avec maman. Hervé est près du bac. Il parle peu. Gwenaëlle veut jouer. On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Gwenaëlle tend le seau. Elle sait attendre. Hervé touche le seau. Il ne dit rien. Gwenaëlle sourit. Elle ne force pas la parole. Plus tard, Sable.</t>
+          <t>Les chaussures de jardin sèchent près du paillasson. Elles sont encore un peu mouillées. Une coccinelle marche sur la rambarde. L'herbe sent le soir qui arrive. Papa cale un arrosoir contre le mur. Maman étend une petite nappe sur le banc. La nappe a des pois blancs. Tu as vu la coccinelle, Chouchou ? Elle marche. L'herbe sent bon, ce soir. En ce moment, Chouchou tient une pelle jaune. Le manche est lisse. Mila est près du bac. Elle parle peu. Elle regarde la terre des pots. Chouchou a envie de jouer. On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. La pelle jaune est dans ta main. Tu peux la tendre. Je tends la pelle. Chouchou tend la pelle. Il sait attendre. Mila touche la pelle. Elle ne dit rien. Chouchou reste près des pots. Une feuille sèche craque sous son pied. Mila prend la pelle. Elle pousse un peu de terre. Bravo, Chouchou. Tu as su attendre. C'est du bon travail. Tu as tendu un jouet. Chouchou pose un seau vert à côté. Mila verse un peu de terre. Un petit tas grandit. Mila ne parle toujours pas. C'est possible. On peut attendre. On ne force pas la parole. Regarder, c'est bien aussi. Un silence. La coccinelle arrive au bout de la rambarde. Puis Mila dit tout bas. Terre. Terre. Ils jouent. Plus tard, maman ouvre la gourde. Un peu d'eau ? Mila secoue la tête. D'accord. D'accord. Regarder, c'est bien aussi. Tu as fini le tas, Chouchou ? Pas encore. Chouchou attend encore. Mila ajoute une pelle de terre. Le jeu a eu lieu, même avec peu de mots.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1329,66 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gwenaëlle est au jardin avec maman. Hervé est près du bac. Il parle peu. Gwenaëlle veut jouer.
-maman|On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole.
-narrateur|Gwenaëlle tend le seau. Elle sait attendre. Hervé touche le seau. Il ne dit rien. Gwenaëlle sourit. Elle ne force pas la parole. Plus tard,
-copain|Sable.</t>
+          <t>narrateur|Les chaussures de jardin sèchent près du paillasson.
+narrateur|Elles sont encore un peu mouillées.
+narrateur|Une coccinelle marche sur la rambarde.
+narrateur|L'herbe sent le soir qui arrive.
+narrateur|Papa cale un arrosoir contre le mur.
+narrateur|Maman étend une petite nappe sur le banc.
+narrateur|La nappe a des pois blancs.
+papa|Tu as vu la coccinelle, Chouchou ?
+enfant-m|Elle marche.
+maman|L'herbe sent bon, ce soir.
+narrateur|En ce moment, Chouchou tient une pelle jaune.
+narrateur|Le manche est lisse.
+narrateur|Mila est près du bac.
+narrateur|Elle parle peu.
+narrateur|Elle regarde la terre des pots.
+narrateur|Chouchou a envie de jouer.
+maman|On peut attendre.
+maman|On n'imite pas.
+maman|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|La pelle jaune est dans ta main.
+papa|Tu peux la tendre.
+enfant-m|Je tends la pelle.
+narrateur|Chouchou tend la pelle.
+narrateur|Il sait attendre.
+narrateur|Mila touche la pelle.
+narrateur|Elle ne dit rien.
+narrateur|Chouchou reste près des pots.
+narrateur|Une feuille sèche craque sous son pied.
+narrateur|Mila prend la pelle.
+narrateur|Elle pousse un peu de terre.
+papa|Bravo, Chouchou.
+papa|Tu as su attendre.
+maman|C'est du bon travail.
+maman|Tu as tendu un jouet.
+narrateur|Chouchou pose un seau vert à côté.
+narrateur|Mila verse un peu de terre.
+narrateur|Un petit tas grandit.
+narrateur|Mila ne parle toujours pas.
+narrateur|C'est possible.
+maman|On peut attendre.
+maman|On ne force pas la parole.
+papa|Regarder, c'est bien aussi.
+narrateur|Un silence.
+narrateur|La coccinelle arrive au bout de la rambarde.
+narrateur|Puis Mila dit tout bas.
+enfant-f|Terre.
+enfant-m|Terre.
+narrateur|Ils jouent.
+narrateur|Plus tard, maman ouvre la gourde.
+maman|Un peu d'eau ?
+narrateur|Mila secoue la tête.
+enfant-m|D'accord.
+papa|D'accord.
+papa|Regarder, c'est bien aussi.
+maman|Tu as fini le tas, Chouchou ?
+enfant-m|Pas encore.
+narrateur|Chouchou attend encore.
+narrateur|Mila ajoute une pelle de terre.
+narrateur|Le jeu a eu lieu, même avec peu de mots.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1343,7 +1416,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hervé parle peu. Que fait Gwenaëlle ?</t>
+          <t>Mila parle peu. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hervé parle peu. Que fait Gwenaëlle ?</t>
+          <t>narrateur|Mila parle peu.
+narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1527,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole.</t>
+          <t>Chouchou a su attendre. Il a tendu un jouet. Il n'a pas forcé la parole. Bravo, Chouchou. Tu as fait du bon travail. Tu as tendu la pelle ? Oui. J'ai attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1745,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gwenaëlle a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole.</t>
+          <t>narrateur|Chouchou a su attendre.
+narrateur|Il a tendu un jouet.
+narrateur|Il n'a pas forcé la parole.
+maman|Bravo, Chouchou.
+maman|Tu as fait du bon travail.
+papa|Tu as tendu la pelle ?
+enfant-m|Oui.
+enfant-m|J'ai attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Gwenaëlle donne la main.</t>
+          <t>Maman range la pelle jaune. Papa reprend l'arrosoir. Chouchou donne la main. On laisse le tas ? Il reste près des pots. Bravo. Les chaussures sèchent encore. La coccinelle s'envole.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1920,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le seau. Gwenaëlle donne la main.</t>
+          <t>narrateur|Maman range la pelle jaune.
+narrateur|Papa reprend l'arrosoir.
+narrateur|Chouchou donne la main.
+maman|On laisse le tas ?
+enfant-m|Il reste près des pots.
+papa|Bravo.
+narrateur|Les chaussures sèchent encore.
+narrateur|La coccinelle s'envole.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai tendu la pelle. On a fait un tas. Bravo. Tu as fait du bon travail. On a su attendre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2095,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai tendu la pelle.
+enfant-m|On a fait un tas.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|On a su attendre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La pelle jaune près des pots</t>
+          <t>La colline de l'escargot</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une pelle jaune attend près des pots. Chouchou la tend à Mila, qui parle peu. Ils font un petit tas de terre. Mila dit : terre.</t>
+          <t>Chouchou veut une colline de terre pour l'escargot de la rambarde. Mila parle peu. Chouchou lui tend la pelle jaune. Elles font la colline. L'escargot avance tout seul.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures de jardin sèchent près du paillasson. Elles sont encore un peu mouillées. Une coccinelle marche sur la rambarde. L'herbe sent le soir qui arrive. Papa cale un arrosoir contre le mur. Maman étend une petite nappe sur le banc. La nappe a des pois blancs. Tu as vu la coccinelle, Chouchou ? Elle marche. L'herbe sent bon, ce soir. En ce moment, Chouchou tient une pelle jaune. Le manche est lisse. Mila est près du bac. Elle parle peu. Elle regarde la terre des pots. Chouchou a envie de jouer. On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. La pelle jaune est dans ta main. Tu peux la tendre. Je tends la pelle. Chouchou tend la pelle. Il sait attendre. Mila touche la pelle. Elle ne dit rien. Chouchou reste près des pots. Une feuille sèche craque sous son pied. Mila prend la pelle. Elle pousse un peu de terre. Bravo, Chouchou. Tu as su attendre. C'est du bon travail. Tu as tendu un jouet. Chouchou pose un seau vert à côté. Mila verse un peu de terre. Un petit tas grandit. Mila ne parle toujours pas. C'est possible. On peut attendre. On ne force pas la parole. Regarder, c'est bien aussi. Un silence. La coccinelle arrive au bout de la rambarde. Puis Mila dit tout bas. Terre. Terre. Ils jouent. Plus tard, maman ouvre la gourde. Un peu d'eau ? Mila secoue la tête. D'accord. D'accord. Regarder, c'est bien aussi. Tu as fini le tas, Chouchou ? Pas encore. Chouchou attend encore. Mila ajoute une pelle de terre. Le jeu a eu lieu, même avec peu de mots.</t>
+          <t>Un escargot avance sur la rambarde. Sa maison brille un peu. L'herbe sent le soir qui arrive. Les chaussures de jardin sont près du mur. Elles sont encore un peu mouillées. Papa cale un arrosoir contre le mur. Maman étend une petite nappe sur le banc. La nappe a des pois blancs. Un coin de nappe vole un peu. Tu as vu l'escargot, Chouchou ? Il avance tout seul. L'herbe sent bon, ce soir. Je veux une colline. Pour sa maison. Une colline de terre ? Oui. Tout près des pots. En ce moment, Chouchou tient la pelle jaune. Le manche est lisse. Un seau vert attend près des pots. La terre est un peu grise. Mila est près du bac. Elle parle peu. Elle regarde la terre des pots. Un caillou gris brille un peu. Chouchou a envie de jouer tout de suite. On peut attendre. Tu peux tendre un jouet. La pelle jaune est dans sa main. Mila ne dit rien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gwenaëlle est au jardin avec maman. Hervé est près du bac. Il parle peu. Gwenaëlle veut jouer. Maman dit : on peut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Gwenaëlle tend le seau. Elle sait attendre. Hervé touche le seau. Il ne dit rien. Gwenaëlle sourit. Elle ne force pas la parole. Plus tard, Hervé dit : sable.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un escargot avance sur la rambarde. Sa maison brille un peu. L'herbe sent le soir qui arrive. Les chaussures de jardin sont près du mur. Elles sont encore un peu mouillées. Papa cale un arrosoir contre le mur. Maman étend une petite nappe sur le banc. La nappe a des pois blancs. Un coin de nappe vole un peu. Tu as vu l'escargot, Chouchou ? Il avance tout seul. L'herbe sent bon, ce soir. Je veux une colline. Pour sa maison. Une colline de terre ? Oui. Tout près des pots. En ce moment, Chouchou tient la pelle jaune. Le manche est lisse. Un seau vert attend près des pots. La terre est un peu grise. Mila est près du bac. Elle parle peu. Elle regarde la terre des pots. Un caillou gris brille un peu. Chouchou a envie de jouer tout de suite. On peut attendre. Tu peux tendre un jouet. La pelle jaune est dans sa main. Mila ne dit rien.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1329,69 +1329,38 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les chaussures de jardin sèchent près du paillasson.
+          <t>narrateur|Un escargot avance sur la rambarde.
+narrateur|Sa maison brille un peu.
+narrateur|L'herbe sent le soir qui arrive.
+narrateur|Les chaussures de jardin sont près du mur.
 narrateur|Elles sont encore un peu mouillées.
-narrateur|Une coccinelle marche sur la rambarde.
-narrateur|L'herbe sent le soir qui arrive.
 narrateur|Papa cale un arrosoir contre le mur.
 narrateur|Maman étend une petite nappe sur le banc.
 narrateur|La nappe a des pois blancs.
-papa|Tu as vu la coccinelle, Chouchou ?
-enfant-m|Elle marche.
+narrateur|Un coin de nappe vole un peu.
+papa|Tu as vu l'escargot, Chouchou ?
+enfant-f|Il avance tout seul.
 maman|L'herbe sent bon, ce soir.
-narrateur|En ce moment, Chouchou tient une pelle jaune.
+enfant-f|Je veux une colline.
+enfant-f|Pour sa maison.
+papa|Une colline de terre ?
+enfant-f|Oui.
+enfant-f|Tout près des pots.
+narrateur|En ce moment, Chouchou tient la pelle jaune.
 narrateur|Le manche est lisse.
+narrateur|Un seau vert attend près des pots.
+narrateur|La terre est un peu grise.
 narrateur|Mila est près du bac.
 narrateur|Elle parle peu.
 narrateur|Elle regarde la terre des pots.
-narrateur|Chouchou a envie de jouer.
+narrateur|Un caillou gris brille un peu.
+narrateur|Chouchou a envie de jouer tout de suite.
 maman|On peut attendre.
-maman|On n'imite pas.
-maman|On peut tendre un jouet.
-maman|On ne force pas la parole.
-papa|La pelle jaune est dans ta main.
-papa|Tu peux la tendre.
-enfant-m|Je tends la pelle.
-narrateur|Chouchou tend la pelle.
-narrateur|Il sait attendre.
-narrateur|Mila touche la pelle.
-narrateur|Elle ne dit rien.
-narrateur|Chouchou reste près des pots.
-narrateur|Une feuille sèche craque sous son pied.
-narrateur|Mila prend la pelle.
-narrateur|Elle pousse un peu de terre.
-papa|Bravo, Chouchou.
-papa|Tu as su attendre.
-maman|C'est du bon travail.
-maman|Tu as tendu un jouet.
-narrateur|Chouchou pose un seau vert à côté.
-narrateur|Mila verse un peu de terre.
-narrateur|Un petit tas grandit.
-narrateur|Mila ne parle toujours pas.
-narrateur|C'est possible.
-maman|On peut attendre.
-maman|On ne force pas la parole.
-papa|Regarder, c'est bien aussi.
-narrateur|Un silence.
-narrateur|La coccinelle arrive au bout de la rambarde.
-narrateur|Puis Mila dit tout bas.
-enfant-f|Terre.
-enfant-m|Terre.
-narrateur|Ils jouent.
-narrateur|Plus tard, maman ouvre la gourde.
-maman|Un peu d'eau ?
-narrateur|Mila secoue la tête.
-enfant-m|D'accord.
-papa|D'accord.
-papa|Regarder, c'est bien aussi.
-maman|Tu as fini le tas, Chouchou ?
-enfant-m|Pas encore.
-narrateur|Chouchou attend encore.
-narrateur|Mila ajoute une pelle de terre.
-narrateur|Le jeu a eu lieu, même avec peu de mots.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tu peux tendre un jouet.
+narrateur|La pelle jaune est dans sa main.
+narrateur|Mila ne dit rien.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1421,7 +1390,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hervé parle peu. Que fait Gwenaëlle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila parle peu. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1436,7 +1405,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>attendre | tendre | le seau | un jouet</t>
+          <t>attendre | tendre | la pelle | un jouet | elle attend</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1451,7 +1420,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle tend un jouet. Elle fait quoi encore ?</t>
+          <t>Elle tend un jouet. Elle attend. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1500,7 +1469,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1576,7 +1545,6 @@
 narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,12 +1569,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a su attendre. Il a tendu un jouet. Il n'a pas forcé la parole. Bravo, Chouchou. Tu as fait du bon travail. Tu as tendu la pelle ? Oui. J'ai attendu.</t>
+          <t>Chouchou tend la pelle. Pour la colline. Elle attend. Une feuille sèche craque sous son pied. Mila touche la pelle. Elle ne dit rien. On ne force pas la parole. L'escargot n'a pas besoin de mots. Mila prend la pelle. Elle pousse un peu de terre. Chouchou pose le seau vert. Mila verse. Un petit tas grandit. La terre est fraîche sous les doigts. Elle sent le soir. La colline. Puis Mila dit tout bas. Terre. Terre. Tu as su attendre. Bravo, Chouchou. L'escargot arrive au bout de la rambarde. Il glisse vers la colline. Ses cornes sortent tout doux. La terre est un peu humide.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gwenaëlle a su &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Elle a tendu un jouet. Elle n'a pas forcé la parole.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou tend la pelle. Pour la colline. Elle attend. Une feuille sèche craque sous son pied. Mila touche la pelle. Elle ne dit rien. On ne force pas la parole. L'escargot n'a pas besoin de mots. Mila prend la pelle. Elle pousse un peu de terre. Chouchou pose le seau vert. Mila verse. Un petit tas grandit. La terre est fraîche sous les doigts. Elle sent le soir. La colline. Puis Mila dit tout bas. Terre. Terre. Tu as su attendre. Bravo, Chouchou. L'escargot arrive au bout de la rambarde. Il glisse vers la colline. Ses cornes sortent tout doux. La terre est un peu humide.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1669,7 +1637,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1745,17 +1713,33 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou a su attendre.
-narrateur|Il a tendu un jouet.
-narrateur|Il n'a pas forcé la parole.
-maman|Bravo, Chouchou.
-maman|Tu as fait du bon travail.
-papa|Tu as tendu la pelle ?
-enfant-m|Oui.
-enfant-m|J'ai attendu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou tend la pelle.
+enfant-f|Pour la colline.
+narrateur|Elle attend.
+narrateur|Une feuille sèche craque sous son pied.
+narrateur|Mila touche la pelle.
+narrateur|Elle ne dit rien.
+maman|On ne force pas la parole.
+papa|L'escargot n'a pas besoin de mots.
+narrateur|Mila prend la pelle.
+narrateur|Elle pousse un peu de terre.
+narrateur|Chouchou pose le seau vert.
+narrateur|Mila verse.
+narrateur|Un petit tas grandit.
+narrateur|La terre est fraîche sous les doigts.
+narrateur|Elle sent le soir.
+enfant-f|La colline.
+narrateur|Puis Mila dit tout bas.
+enfant-f|Terre.
+enfant-f|Terre.
+papa|Tu as su attendre.
+papa|Bravo, Chouchou.
+narrateur|L'escargot arrive au bout de la rambarde.
+narrateur|Il glisse vers la colline.
+narrateur|Ses cornes sortent tout doux.
+narrateur|La terre est un peu humide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1780,12 +1764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range la pelle jaune. Papa reprend l'arrosoir. Chouchou donne la main. On laisse le tas ? Il reste près des pots. Bravo. Les chaussures sèchent encore. La coccinelle s'envole.</t>
+          <t>Maman ouvre la gourde. L'eau sent le plastique tiède. Un peu d'eau ? Mila secoue la tête. D'accord. D'accord. Tu as fini la colline, Chouchou ? Oui, maman. Il grimpe dessus. Maman range la nappe à pois. Les pois sont un peu sablés. Papa reprend l'arrosoir. Chouchou donne la main. Les chaussures sèchent encore. L'escargot reste sur la colline. Sa maison brille encore un peu. Il avance tout seul. Oui. Tout seul. L'herbe est plus fraîche.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le seau. Gwenaëlle donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman ouvre la gourde. L'eau sent le plastique tiède. Un peu d'eau ? Mila secoue la tête. D'accord. D'accord. Tu as fini la colline, Chouchou ? Oui, maman. Il grimpe dessus. Maman range la nappe à pois. Les pois sont un peu sablés. Papa reprend l'arrosoir. Chouchou donne la main. Les chaussures sèchent encore. L'escargot reste sur la colline. Sa maison brille encore un peu. Il avance tout seul. Oui. Tout seul. L'herbe est plus fraîche.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1848,7 +1832,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1920,17 +1904,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range la pelle jaune.
+          <t>narrateur|Maman ouvre la gourde.
+narrateur|L'eau sent le plastique tiède.
+maman|Un peu d'eau ?
+narrateur|Mila secoue la tête.
+enfant-f|D'accord.
+papa|D'accord.
+maman|Tu as fini la colline, Chouchou ?
+enfant-f|Oui, maman.
+enfant-f|Il grimpe dessus.
+narrateur|Maman range la nappe à pois.
+narrateur|Les pois sont un peu sablés.
 narrateur|Papa reprend l'arrosoir.
 narrateur|Chouchou donne la main.
-maman|On laisse le tas ?
-enfant-m|Il reste près des pots.
-papa|Bravo.
-narrateur|Les chaussures sèchent encore.
-narrateur|La coccinelle s'envole.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+papa|Les chaussures sèchent encore.
+narrateur|L'escargot reste sur la colline.
+narrateur|Sa maison brille encore un peu.
+enfant-f|Il avance tout seul.
+maman|Oui.
+maman|Tout seul.
+narrateur|L'herbe est plus fraîche.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai tendu la pelle. On a fait un tas. Bravo. Tu as fait du bon travail. On a su attendre. L'histoire est finie.</t>
+          <t>L'escargot a sa colline. Près des pots. Sa maison brille encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'escargot a sa colline. Près des pots. Sa maison brille encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2016,14 +2011,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2095,15 +2090,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai tendu la pelle.
-enfant-m|On a fait un tas.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-papa|On a su attendre.
+          <t>enfant-f|L'escargot a sa colline.
+maman|Près des pots.
+papa|Sa maison brille encore.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
@@ -1950,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'escargot a sa colline. Près des pots. Sa maison brille encore. L'histoire est finie.</t>
+          <t>L'escargot a sa colline. Près des pots. Sa maison brille encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>L'escargot a sa colline. Près des pots. Sa maison brille encore. L'histoire est finie.</t>
+          <t>L'escargot a sa colline. Près des pots. Sa maison brille encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,8 +2092,7 @@
         <is>
           <t>enfant-f|L'escargot a sa colline.
 maman|Près des pots.
-papa|Sa maison brille encore.
-narrateur|L'histoire est finie.</t>
+papa|Sa maison brille encore.</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2163,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, soir, rambarde</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gwenaëlle, Hervé, maman</t>
+          <t>Chouchou, Mila, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-07.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La colline de l'escargot</t>
+          <t>La pelle jaune près des pots</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin, soir, rambarde</t>
+          <t>jardin, chaussures, paillasson, coccinelle, rambarde, pelle jaune, pots</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chouchou veut une colline de terre pour l'escargot de la rambarde. Mila parle peu. Chouchou lui tend la pelle jaune. Elles font la colline. L'escargot avance tout seul.</t>
+          <t>Les semelles tapent le paillasson. Une coccinelle avance sur la rambarde. Près d'elle, un éclat de rambarde brille. Chouchou veut la pelle jaune, maintenant, pour le pot. Mila ne dit rien. Trop vite, la pelle tape un pot. Sourire parti, poitrine, papa accroupi. Elle refuse de foncer, attend, tend la pelle. Merci vécu. Second pot trop vite. Un éclat de rambarde tient sur le fer.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un escargot avance sur la rambarde. Sa maison brille un peu. L'herbe sent le soir qui arrive. Les chaussures de jardin sont près du mur. Elles sont encore un peu mouillées. Papa cale un arrosoir contre le mur. Maman étend une petite nappe sur le banc. La nappe a des pois blancs. Un coin de nappe vole un peu. Tu as vu l'escargot, Chouchou ? Il avance tout seul. L'herbe sent bon, ce soir. Je veux une colline. Pour sa maison. Une colline de terre ? Oui. Tout près des pots. En ce moment, Chouchou tient la pelle jaune. Le manche est lisse. Un seau vert attend près des pots. La terre est un peu grise. Mila est près du bac. Elle parle peu. Elle regarde la terre des pots. Un caillou gris brille un peu. Chouchou a envie de jouer tout de suite. On peut attendre. Tu peux tendre un jouet. La pelle jaune est dans sa main. Mila ne dit rien.</t>
+          <t>Les semelles tapent le paillasson. Ça fait un bruit de paille sèche. Ça gratte, papa. Tes chaussures, Chouchou ? Oui, papa. Le paillasson sent l'herbe tiède. Maman pose les chaussures près du mur. Les semelles sont un peu poussiéreuses. Tu les sens, les chaussures ? Elles sentent le jardin. Une coccinelle avance sur la rambarde. Elle marche, maman. Tu la vois, la petite bête ? Oui, rouge. Près d'elle, un éclat de rambarde brille. Il brille, papa. Tu le vois, le petit point ? Oui, un petit point. Un pot terreux attend près du mur. La terre est grise, un peu sèche. Je veux la pelle, maintenant ! Pour le pot, tout de suite. La pelle jaune, là ? Oui, la jaune. Le pot est près du mur ? Il doit se remplir. En ce moment, Chouchou tient la pelle jaune. Le manche est lisse. Tu la tiens, Chouchou ? Oui. La porte du jardin s'ouvre. Mila arrive près des pots. Elle regarde le sol. Elle ne dit rien. Tu creuses avec moi ? Mila serre les mains. Chouchou a envie de tout raconter. Les mots montent très vite. La coccinelle ! Le pot ! La pelle ! Chouchou pousse trop vite vers elle. La pelle tape un pot. Oh. Le pot penche sur le paillasson. Le pot. Le sourire de Chouchou disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Mila, Chouchou ? Oui, papa. Tes mains tiennent la pelle, Chouchou ? Un peu, maman. L'éclat de rambarde tremble, puis tient. Mila reste près des pots. Elle ne dit rien, papa. Chouchou regarde papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un escargot avance sur la rambarde. Sa maison brille un peu. L'herbe sent le soir qui arrive. Les chaussures de jardin sont près du mur. Elles sont encore un peu mouillées. Papa cale un arrosoir contre le mur. Maman étend une petite nappe sur le banc. La nappe a des pois blancs. Un coin de nappe vole un peu. Tu as vu l'escargot, Chouchou ? Il avance tout seul. L'herbe sent bon, ce soir. Je veux une colline. Pour sa maison. Une colline de terre ? Oui. Tout près des pots. En ce moment, Chouchou tient la pelle jaune. Le manche est lisse. Un seau vert attend près des pots. La terre est un peu grise. Mila est près du bac. Elle parle peu. Elle regarde la terre des pots. Un caillou gris brille un peu. Chouchou a envie de jouer tout de suite. On peut attendre. Tu peux tendre un jouet. La pelle jaune est dans sa main. Mila ne dit rien.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Les semelles tapent le paillasson. Ça fait un bruit de paille sèche. Ça gratte, papa. Tes chaussures, Chouchou ? Oui, papa. Le paillasson sent l'herbe tiède. Maman pose les chaussures près du mur. Les semelles sont un peu poussiéreuses. Tu les sens, les chaussures ? Elles sentent le jardin. Une coccinelle avance sur la rambarde. Elle marche, maman. Tu la vois, la petite bête ? Oui, rouge. Près d'elle, un &lt;emphasis level="moderate"&gt;éclat de rambarde&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, le petit point ? Oui, un petit point. Un pot terreux attend près du mur. La terre est grise, un peu sèche. Je veux la pelle, maintenant ! Pour le pot, tout de suite. La pelle jaune, là ? Oui, la jaune. Le pot est près du mur ? Il doit se remplir. En ce moment, Chouchou tient la pelle jaune. Le manche est lisse. Tu la tiens, Chouchou ? Oui. La porte du jardin s'ouvre. Mila arrive près des pots. Elle regarde le sol. Elle ne dit rien. Tu creuses avec moi ? Mila serre les mains. Chouchou a envie de tout raconter. Les mots montent très vite. La coccinelle ! Le pot ! La pelle ! Chouchou pousse trop vite vers elle. La pelle tape un pot. Oh. Le pot penche sur le paillasson. Le pot. Le sourire de Chouchou disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Mila, Chouchou ? Oui, papa. Tes mains tiennent la pelle, Chouchou ? Un peu, maman. L'éclat de rambarde tremble, puis tient. Mila reste près des pots. Elle ne dit rien, papa. Chouchou regarde papa.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle est au jardin avec maman. Hervé est près du bac. Il parle peu. Gwenaëlle veut jouer. Maman dit : on peut &lt;emphasis&gt;attendre&lt;/emphasis&gt;. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Gwenaëlle tend le seau. Elle sait attendre. Hervé touche le seau. Il ne dit rien. Gwenaëlle sourit. Elle ne force pas la parole. Plus tard, Hervé dit : sable. [pause]</t>
+          <t>Les semelles tapent le paillasson. Ça fait un bruit de paille sèche. Ça gratte, papa. Tes chaussures, Chouchou ? Oui, papa. Le paillasson sent l'herbe tiède. Maman pose les chaussures près du mur. Les semelles sont un peu poussiéreuses. Tu les sens, les chaussures ? Elles sentent le jardin. Une coccinelle avance sur la rambarde. Elle marche, maman. Tu la vois, la petite bête ? Oui, rouge. Près d'elle, un &lt;emphasis&gt;éclat de rambarde&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, le petit point ? Oui, un petit point. Un pot terreux attend près du mur. La terre est grise, un peu sèche. Je veux la pelle, maintenant ! Pour le pot, tout de suite. La pelle jaune, là ? Oui, la jaune. Le pot est près du mur ? Il doit se remplir. En ce moment, Chouchou tient la pelle jaune. Le manche est lisse. Tu la tiens, Chouchou ? Oui. La porte du jardin s'ouvre. Mila arrive près des pots. Elle regarde le sol. Elle ne dit rien. Tu creuses avec moi ? Mila serre les mains. Chouchou a envie de tout raconter. Les mots montent très vite. La coccinelle ! Le pot ! La pelle ! Chouchou pousse trop vite vers elle. La pelle tape un pot. Oh. Le pot penche sur le paillasson. Le pot. Le sourire de Chouchou disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Mila, Chouchou ? Oui, papa. Tes mains tiennent la pelle, Chouchou ? Un peu, maman. L'éclat de rambarde tremble, puis tient. Mila reste près des pots. Elle ne dit rien, papa. Chouchou regarde papa. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>attendre</t>
+          <t>éclat de rambarde</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,39 +1326,76 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_la_pelle_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un escargot avance sur la rambarde.
-narrateur|Sa maison brille un peu.
-narrateur|L'herbe sent le soir qui arrive.
-narrateur|Les chaussures de jardin sont près du mur.
-narrateur|Elles sont encore un peu mouillées.
-narrateur|Papa cale un arrosoir contre le mur.
-narrateur|Maman étend une petite nappe sur le banc.
-narrateur|La nappe a des pois blancs.
-narrateur|Un coin de nappe vole un peu.
-papa|Tu as vu l'escargot, Chouchou ?
-enfant-f|Il avance tout seul.
-maman|L'herbe sent bon, ce soir.
-enfant-f|Je veux une colline.
-enfant-f|Pour sa maison.
-papa|Une colline de terre ?
+          <t>narrateur|Les semelles tapent le paillasson.
+narrateur|Ça fait un bruit de paille sèche.
+enfant-f|Ça gratte, papa.
+papa|Tes chaussures, Chouchou ?
+enfant-f|Oui, papa.
+narrateur|Le paillasson sent l'herbe tiède.
+narrateur|Maman pose les chaussures près du mur.
+narrateur|Les semelles sont un peu poussiéreuses.
+maman|Tu les sens, les chaussures ?
+enfant-f|Elles sentent le jardin.
+narrateur|Une coccinelle avance sur la rambarde.
+enfant-f|Elle marche, maman.
+maman|Tu la vois, la petite bête ?
+enfant-f|Oui, rouge.
+narrateur|Près d'elle, un éclat de rambarde brille.
+enfant-f|Il brille, papa.
+papa|Tu le vois, le petit point ?
+enfant-f|Oui, un petit point.
+narrateur|Un pot terreux attend près du mur.
+narrateur|La terre est grise, un peu sèche.
+enfant-f|Je veux la pelle, maintenant !
+enfant-f|Pour le pot, tout de suite.
+papa|La pelle jaune, là ?
+enfant-f|Oui, la jaune.
+maman|Le pot est près du mur ?
+enfant-f|Il doit se remplir.
+narrateur|En ce moment, Chouchou tient la pelle jaune.
+enfant-f|Le manche est lisse.
+papa|Tu la tiens, Chouchou ?
 enfant-f|Oui.
-enfant-f|Tout près des pots.
-narrateur|En ce moment, Chouchou tient la pelle jaune.
-narrateur|Le manche est lisse.
-narrateur|Un seau vert attend près des pots.
-narrateur|La terre est un peu grise.
-narrateur|Mila est près du bac.
-narrateur|Elle parle peu.
-narrateur|Elle regarde la terre des pots.
-narrateur|Un caillou gris brille un peu.
-narrateur|Chouchou a envie de jouer tout de suite.
-maman|On peut attendre.
-papa|Tu peux tendre un jouet.
-narrateur|La pelle jaune est dans sa main.
-narrateur|Mila ne dit rien.</t>
+narrateur|La porte du jardin s'ouvre.
+narrateur|Mila arrive près des pots.
+narrateur|Elle regarde le sol.
+narrateur|Elle ne dit rien.
+enfant-f|Tu creuses avec moi ?
+narrateur|Mila serre les mains.
+narrateur|Chouchou a envie de tout raconter.
+narrateur|Les mots montent très vite.
+enfant-f|La coccinelle !
+enfant-f|Le pot !
+enfant-f|La pelle !
+narrateur|Chouchou pousse trop vite vers elle.
+narrateur|La pelle tape un pot.
+enfant-f|Oh.
+narrateur|Le pot penche sur le paillasson.
+enfant-f|Le pot.
+narrateur|Le sourire de Chouchou disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu vois Mila, Chouchou ?
+enfant-f|Oui, papa.
+maman|Tes mains tiennent la pelle, Chouchou ?
+enfant-f|Un peu, maman.
+narrateur|L'éclat de rambarde tremble, puis tient.
+narrateur|Mila reste près des pots.
+enfant-f|Elle ne dit rien, papa.
+narrateur|Chouchou regarde papa.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>paillasson</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1427,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mila parle peu. Que fait Chouchou ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mila parle peu. Que fait &lt;emphasis level="moderate"&gt;Chouchou&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Hervé parle peu. Que fait Gwenaëlle ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Mila parle peu. Que fait &lt;emphasis&gt;Chouchou&lt;/emphasis&gt; ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1458,7 +1495,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1469,7 +1506,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1484,34 +1521,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>Chouchou</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1526,17 +1567,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=mila_parle_peu_que_fait_chouchou; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1569,17 +1610,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou tend la pelle. Pour la colline. Elle attend. Une feuille sèche craque sous son pied. Mila touche la pelle. Elle ne dit rien. On ne force pas la parole. L'escargot n'a pas besoin de mots. Mila prend la pelle. Elle pousse un peu de terre. Chouchou pose le seau vert. Mila verse. Un petit tas grandit. La terre est fraîche sous les doigts. Elle sent le soir. La colline. Puis Mila dit tout bas. Terre. Terre. Tu as su attendre. Bravo, Chouchou. L'escargot arrive au bout de la rambarde. Il glisse vers la colline. Ses cornes sortent tout doux. La terre est un peu humide.</t>
+          <t>Chouchou veut la pelle, tout de suite. Je la pousse, maintenant ! Elle avance trop vite vers Mila. Les mots se bousculent dans sa bouche. Mila baisse les yeux. Elle serre les mains contre elle. Oh. Le sourire ne revient pas. Chouchou refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe la pelle, un instant. Elle écoute la coccinelle sur le fer. Tu veux le pot avec Mila ? Papa reste à la même hauteur. Papa, on fait quoi ? On pose la pelle, puis on reste. D'accord. Chouchou reste un moment, les mains ouvertes. Elle attend. Elle tend la pelle. Pour toi. Mila ne dit rien. Elle prend la pelle, sans parler. Oui. Chouchou pose les mains près du pot. Elle reste, sans se presser. Mila pousse la terre, plus lentement. Merci, Chouchou. Papa a vu les deux, près des pots. La terre est tiède, sous les doigts. Elle est chaude. Le pot se remplit, un peu de travers. Le pot. Il a de la terre, là ? Oui, là. Chouchou glisse la main sur le bord. L'argile est douce, contre la peau. Tes mains sont au chaud, Chouchou ? Un peu, maman. Mila s'assoit, puis se relève. Terre. On va jusqu'au bord ? Le pot va jusqu'au paillasson. Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou tend la pelle. Pour la colline. Elle attend. Une feuille sèche craque sous son pied. Mila touche la pelle. Elle ne dit rien. On ne force pas la parole. L'escargot n'a pas besoin de mots. Mila prend la pelle. Elle pousse un peu de terre. Chouchou pose le seau vert. Mila verse. Un petit tas grandit. La terre est fraîche sous les doigts. Elle sent le soir. La colline. Puis Mila dit tout bas. Terre. Terre. Tu as su attendre. Bravo, Chouchou. L'escargot arrive au bout de la rambarde. Il glisse vers la colline. Ses cornes sortent tout doux. La terre est un peu humide.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Chouchou veut la &lt;emphasis level="moderate"&gt;pelle&lt;/emphasis&gt;, tout de suite. Je la pousse, maintenant ! Elle avance trop vite vers Mila. Les mots se bousculent dans sa bouche. Mila baisse les yeux. Elle serre les mains contre elle. Oh. Le sourire ne revient pas. Chouchou refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe la pelle, un instant. Elle écoute la coccinelle sur le fer. Tu veux le pot avec Mila ? Papa reste à la même hauteur. Papa, on fait quoi ? On pose la pelle, puis on reste. D'accord. Chouchou reste un moment, les mains ouvertes. Elle attend. Elle tend la pelle. Pour toi. Mila ne dit rien. Elle prend la pelle, sans parler. Oui. Chouchou pose les mains près du pot. Elle reste, sans se presser. Mila pousse la terre, plus lentement. Merci, Chouchou. Papa a vu les deux, près des pots. La terre est tiède, sous les doigts. Elle est chaude. Le pot se remplit, un peu de travers. Le pot. Il a de la terre, là ? Oui, là. Chouchou glisse la main sur le bord. L'argile est douce, contre la peau. Tes mains sont au chaud, Chouchou ? Un peu, maman. Mila s'assoit, puis se relève. Terre. On va jusqu'au bord ? Le pot va jusqu'au paillasson. Oui, maman.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle a su &lt;emphasis&gt;attendre&lt;/emphasis&gt;. Elle a tendu un jouet. Elle n'a pas forcé la parole. [pause]</t>
+          <t>Chouchou veut la &lt;emphasis&gt;pelle&lt;/emphasis&gt;, tout de suite. Je la pousse, maintenant ! Elle avance trop vite vers Mila. Les mots se bousculent dans sa bouche. Mila baisse les yeux. Elle serre les mains contre elle. Oh. Le sourire ne revient pas. Chouchou refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe la pelle, un instant. Elle écoute la coccinelle sur le fer. Tu veux le pot avec Mila ? Papa reste à la même hauteur. Papa, on fait quoi ? On pose la pelle, puis on reste. D'accord. Chouchou reste un moment, les mains ouvertes. Elle attend. Elle tend la pelle. Pour toi. Mila ne dit rien. Elle prend la pelle, sans parler. Oui. Chouchou pose les mains près du pot. Elle reste, sans se presser. Mila pousse la terre, plus lentement. Merci, Chouchou. Papa a vu les deux, près des pots. La terre est tiède, sous les doigts. Elle est chaude. Le pot se remplit, un peu de travers. Le pot. Il a de la terre, là ? Oui, là. Chouchou glisse la main sur le bord. L'argile est douce, contre la peau. Tes mains sont au chaud, Chouchou ? Un peu, maman. Mila s'assoit, puis se relève. Terre. On va jusqu'au bord ? Le pot va jusqu'au paillasson. Oui, maman. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1626,7 +1667,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1634,10 +1675,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1660,30 +1701,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>attendre</t>
+          <t>pelle</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1692,10 +1733,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1708,36 +1749,61 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_attend_tend; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou tend la pelle.
-enfant-f|Pour la colline.
+          <t>narrateur|Chouchou veut la pelle, tout de suite.
+enfant-f|Je la pousse, maintenant !
+narrateur|Elle avance trop vite vers Mila.
+narrateur|Les mots se bousculent dans sa bouche.
+narrateur|Mila baisse les yeux.
+narrateur|Elle serre les mains contre elle.
+enfant-f|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Chouchou refuse de foncer.
+narrateur|Elle referme la bouche.
+narrateur|Personne ne parle.
+narrateur|Elle observe la pelle, un instant.
+narrateur|Elle écoute la coccinelle sur le fer.
+papa|Tu veux le pot avec Mila ?
+narrateur|Papa reste à la même hauteur.
+enfant-f|Papa, on fait quoi ?
+papa|On pose la pelle, puis on reste.
+enfant-f|D'accord.
+narrateur|Chouchou reste un moment, les mains ouvertes.
 narrateur|Elle attend.
-narrateur|Une feuille sèche craque sous son pied.
-narrateur|Mila touche la pelle.
-narrateur|Elle ne dit rien.
-maman|On ne force pas la parole.
-papa|L'escargot n'a pas besoin de mots.
-narrateur|Mila prend la pelle.
-narrateur|Elle pousse un peu de terre.
-narrateur|Chouchou pose le seau vert.
-narrateur|Mila verse.
-narrateur|Un petit tas grandit.
-narrateur|La terre est fraîche sous les doigts.
-narrateur|Elle sent le soir.
-enfant-f|La colline.
-narrateur|Puis Mila dit tout bas.
-enfant-f|Terre.
-enfant-f|Terre.
-papa|Tu as su attendre.
-papa|Bravo, Chouchou.
-narrateur|L'escargot arrive au bout de la rambarde.
-narrateur|Il glisse vers la colline.
-narrateur|Ses cornes sortent tout doux.
-narrateur|La terre est un peu humide.</t>
+narrateur|Elle tend la pelle.
+enfant-f|Pour toi.
+narrateur|Mila ne dit rien.
+narrateur|Elle prend la pelle, sans parler.
+copine|Oui.
+narrateur|Chouchou pose les mains près du pot.
+narrateur|Elle reste, sans se presser.
+narrateur|Mila pousse la terre, plus lentement.
+papa|Merci, Chouchou.
+narrateur|Papa a vu les deux, près des pots.
+maman|La terre est tiède, sous les doigts.
+enfant-f|Elle est chaude.
+narrateur|Le pot se remplit, un peu de travers.
+enfant-f|Le pot.
+papa|Il a de la terre, là ?
+enfant-f|Oui, là.
+narrateur|Chouchou glisse la main sur le bord.
+narrateur|L'argile est douce, contre la peau.
+maman|Tes mains sont au chaud, Chouchou ?
+enfant-f|Un peu, maman.
+narrateur|Mila s'assoit, puis se relève.
+copine|Terre.
+enfant-f|On va jusqu'au bord ?
+maman|Le pot va jusqu'au paillasson.
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>pots</t>
         </is>
       </c>
     </row>
@@ -1764,17 +1830,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman ouvre la gourde. L'eau sent le plastique tiède. Un peu d'eau ? Mila secoue la tête. D'accord. D'accord. Tu as fini la colline, Chouchou ? Oui, maman. Il grimpe dessus. Maman range la nappe à pois. Les pois sont un peu sablés. Papa reprend l'arrosoir. Chouchou donne la main. Les chaussures sèchent encore. L'escargot reste sur la colline. Sa maison brille encore un peu. Il avance tout seul. Oui. Tout seul. L'herbe est plus fraîche.</t>
+          <t>Ils restent près des pots. Un second pot attend, vide. Il se remplit, maintenant ! Chouchou pousse trop vite. La terre penche vers le paillasson. Ça tombe ! Mila tend les mains, sans parler. Chouchou avance les mains, trop vite. Puis elle s'arrête net. Chouchou refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe la pelle, un instant. Elle écoute le silence du jardin. Sur la rambarde, un éclat de rambarde luit. Là, sur le fer. Tu prends la pelle, Mila ? Mila ne dit rien. Elle tend les mains, sans parler. Oui. Chouchou pousse la pelle, sans se presser. Mila la reçoit, plus lentement. Le manche est lisse et tiède. Tu la vois, la pelle ? Oui, papa. Les pots sont près du paillasson ? Oui, maman. La terre entre dans le second pot. Chouchou pose une main sur le bord. Mila pose la suivante. Le pot tient, Chouchou ? Oui, papa. Une coccinelle passe sur la rambarde. Elle reste sur le fer.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman ouvre la gourde. L'eau sent le plastique tiède. Un peu d'eau ? Mila secoue la tête. D'accord. D'accord. Tu as fini la colline, Chouchou ? Oui, maman. Il grimpe dessus. Maman range la nappe à pois. Les pois sont un peu sablés. Papa reprend l'arrosoir. Chouchou donne la main. Les chaussures sèchent encore. L'escargot reste sur la colline. Sa maison brille encore un peu. Il avance tout seul. Oui. Tout seul. L'herbe est plus fraîche.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ils restent près des pots. Un second pot attend, vide. Il se remplit, maintenant ! Chouchou pousse trop vite. La terre penche vers le paillasson. Ça tombe ! Mila tend les mains, sans parler. Chouchou avance les mains, trop vite. Puis elle s'arrête net. Chouchou refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe la pelle, un instant. Elle écoute le silence du jardin. Sur la rambarde, un &lt;emphasis level="moderate"&gt;éclat de rambarde&lt;/emphasis&gt; luit. Là, sur le fer. Tu prends la pelle, Mila ? Mila ne dit rien. Elle tend les mains, sans parler. Oui. Chouchou pousse la pelle, sans se presser. Mila la reçoit, plus lentement. Le manche est lisse et tiède. Tu la vois, la pelle ? Oui, papa. Les pots sont près du paillasson ? Oui, maman. La terre entre dans le second pot. Chouchou pose une main sur le bord. Mila pose la suivante. Le pot tient, Chouchou ? Oui, papa. Une coccinelle passe sur la rambarde. Elle reste sur le fer.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Gwenaëlle donne la &lt;emphasis&gt;main&lt;/emphasis&gt;. [pause]</t>
+          <t>Ils restent près des pots. Un second pot attend, vide. Il se remplit, maintenant ! Chouchou pousse trop vite. La terre penche vers le paillasson. Ça tombe ! Mila tend les mains, sans parler. Chouchou avance les mains, trop vite. Puis elle s'arrête net. Chouchou refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe la pelle, un instant. Elle écoute le silence du jardin. Sur la rambarde, un &lt;emphasis&gt;éclat de rambarde&lt;/emphasis&gt; luit. Là, sur le fer. Tu prends la pelle, Mila ? Mila ne dit rien. Elle tend les mains, sans parler. Oui. Chouchou pousse la pelle, sans se presser. Mila la reçoit, plus lentement. Le manche est lisse et tiède. Tu la vois, la pelle ? Oui, papa. Les pots sont près du paillasson ? Oui, maman. La terre entre dans le second pot. Chouchou pose une main sur le bord. Mila pose la suivante. Le pot tient, Chouchou ? Oui, papa. Une coccinelle passe sur la rambarde. Elle reste sur le fer. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1821,7 +1887,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1829,10 +1895,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1855,30 +1921,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>éclat de rambarde</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1887,10 +1953,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1901,29 +1967,52 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=second_pot_trop_vite_elle_attend; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman ouvre la gourde.
-narrateur|L'eau sent le plastique tiède.
-maman|Un peu d'eau ?
-narrateur|Mila secoue la tête.
-enfant-f|D'accord.
-papa|D'accord.
-maman|Tu as fini la colline, Chouchou ?
+          <t>narrateur|Ils restent près des pots.
+narrateur|Un second pot attend, vide.
+enfant-f|Il se remplit, maintenant !
+narrateur|Chouchou pousse trop vite.
+narrateur|La terre penche vers le paillasson.
+enfant-f|Ça tombe !
+narrateur|Mila tend les mains, sans parler.
+narrateur|Chouchou avance les mains, trop vite.
+narrateur|Puis elle s'arrête net.
+narrateur|Chouchou refuse de foncer, cette fois.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Personne ne dit la suite.
+narrateur|Elle observe la pelle, un instant.
+narrateur|Elle écoute le silence du jardin.
+narrateur|Sur la rambarde, un éclat de rambarde luit.
+enfant-f|Là, sur le fer.
+enfant-f|Tu prends la pelle, Mila ?
+narrateur|Mila ne dit rien.
+narrateur|Elle tend les mains, sans parler.
+copine|Oui.
+narrateur|Chouchou pousse la pelle, sans se presser.
+narrateur|Mila la reçoit, plus lentement.
+narrateur|Le manche est lisse et tiède.
+papa|Tu la vois, la pelle ?
+enfant-f|Oui, papa.
+maman|Les pots sont près du paillasson ?
 enfant-f|Oui, maman.
-enfant-f|Il grimpe dessus.
-narrateur|Maman range la nappe à pois.
-narrateur|Les pois sont un peu sablés.
-narrateur|Papa reprend l'arrosoir.
-narrateur|Chouchou donne la main.
-papa|Les chaussures sèchent encore.
-narrateur|L'escargot reste sur la colline.
-narrateur|Sa maison brille encore un peu.
-enfant-f|Il avance tout seul.
-maman|Oui.
-maman|Tout seul.
-narrateur|L'herbe est plus fraîche.</t>
+narrateur|La terre entre dans le second pot.
+narrateur|Chouchou pose une main sur le bord.
+narrateur|Mila pose la suivante.
+papa|Le pot tient, Chouchou ?
+enfant-f|Oui, papa.
+maman|Une coccinelle passe sur la rambarde.
+enfant-f|Elle reste sur le fer.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>pelle</t>
         </is>
       </c>
     </row>
@@ -1950,17 +2039,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'escargot a sa colline. Près des pots. Sa maison brille encore.</t>
+          <t>Ils restent près des pots. Le pot est rempli, Chouchou ? Oui, maman. Tu souffles un peu ? Oui, papa. Chouchou souffle, un filet d'air. La terre sent bon. Tu la sens, la terre ? Oui, maman. Le pot reste un peu, de travers. Il a tenu, près des pots. Terre. Le paillasson est chaud, sous les mains. La pelle jaune fait de l'ombre. On y retourne, après. Un éclat de rambarde tient sur le fer.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>L'escargot a sa colline. Près des pots. Sa maison brille encore.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent près des pots. Le pot est rempli, Chouchou ? Oui, maman. Tu souffles un peu ? Oui, papa. Chouchou souffle, un filet d'air. La terre sent bon. Tu la sens, la terre ? Oui, maman. Le pot reste un peu, de travers. Il a tenu, près des pots. Terre. Le paillasson est chaud, sous les mains. La pelle jaune fait de l'ombre. On y retourne, après. Un &lt;emphasis level="moderate"&gt;éclat de rambarde&lt;/emphasis&gt; tient sur le fer.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent près des pots. Le pot est rempli, Chouchou ? Oui, maman. Tu souffles un peu ? Oui, papa. Chouchou souffle, un filet d'air. La terre sent bon. Tu la sens, la terre ? Oui, maman. Le pot reste un peu, de travers. Il a tenu, près des pots. Terre. Le paillasson est chaud, sous les mains. La pelle jaune fait de l'ombre. On y retourne, après. Un &lt;emphasis&gt;éclat de rambarde&lt;/emphasis&gt; tient sur le fer.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2007,15 +2096,15 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>1.28</v>
@@ -2027,12 +2116,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2041,17 +2130,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de rambarde</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2060,11 +2153,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2073,26 +2166,43 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_le_fer; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|L'escargot a sa colline.
-maman|Près des pots.
-papa|Sa maison brille encore.</t>
+          <t>narrateur|Ils restent près des pots.
+maman|Le pot est rempli, Chouchou ?
+enfant-f|Oui, maman.
+papa|Tu souffles un peu ?
+enfant-f|Oui, papa.
+narrateur|Chouchou souffle, un filet d'air.
+enfant-f|La terre sent bon.
+maman|Tu la sens, la terre ?
+enfant-f|Oui, maman.
+papa|Le pot reste un peu, de travers.
+enfant-f|Il a tenu, près des pots.
+copine|Terre.
+narrateur|Le paillasson est chaud, sous les mains.
+narrateur|La pelle jaune fait de l'ombre.
+enfant-f|On y retourne, après.
+narrateur|Un éclat de rambarde tient sur le fer.</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2280,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
